--- a/Investment_Strategy/Config/parameters_datacurator.xlsx
+++ b/Investment_Strategy/Config/parameters_datacurator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PoC\PoC_Data-Curator-Features\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588EB03F-72FA-4778-9DCE-6B4C0208C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89306041-E22F-42EC-A78A-0C91D28DA007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="231">
   <si>
     <t>parameter</t>
   </si>
@@ -279,9 +279,6 @@
     <t>info</t>
   </si>
   <si>
-    <t>0.40.0</t>
-  </si>
-  <si>
     <t>main_identifier</t>
   </si>
   <si>
@@ -782,28 +779,13 @@
     <t>c_simple_moving_average_252d_close_split_adjusted</t>
   </si>
   <si>
-    <t>c_50_sma</t>
-  </si>
-  <si>
-    <t>c_200_sma</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>c_sma_signal</t>
   </si>
   <si>
-    <t>c_weighted_average_basic_shares_outstanding_outlier_adjusted</t>
-  </si>
-  <si>
-    <t>c_weighted_average_diluted_shares_outstanding_outlier_adjusted</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>yahoo_finance</t>
-  </si>
-  <si>
-    <t>SPY</t>
+    <t>financial_modeling_prep</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>63</v>
@@ -1444,7 +1426,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>64</v>
@@ -1455,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="16">
-        <v>1</v>
+        <v>36526</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>6</v>
@@ -1466,7 +1448,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="16">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>8</v>
@@ -1515,7 +1497,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>18</v>
@@ -1530,10 +1512,10 @@
   <dataConsolidate/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"financial_modeling_prep,yahoo_finance"</formula1>
+      <formula1>"financial_modeling_prep,yahoo_finance, lseg_workspace"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"financial_modeling_prep,none"</formula1>
+      <formula1>"financial_modeling_prep,lseg_workspace,none"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>B4</formula1>
@@ -1555,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="4" customWidth="1"/>
@@ -1565,15 +1547,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>68</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B207"/>
+  <dimension ref="A1:B205"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="73.42578125" style="4" customWidth="1"/>
@@ -1643,68 +1620,68 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="18"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1724,28 +1701,28 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="20"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1760,52 +1737,52 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
@@ -1820,22 +1797,22 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
@@ -1845,57 +1822,57 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
@@ -1920,37 +1897,37 @@
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
@@ -1960,52 +1937,52 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
@@ -2015,27 +1992,27 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
@@ -2050,7 +2027,7 @@
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
@@ -2060,52 +2037,52 @@
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
@@ -2115,37 +2092,37 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
@@ -2155,27 +2132,27 @@
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
@@ -2185,162 +2162,162 @@
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
@@ -2350,7 +2327,7 @@
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
@@ -2360,7 +2337,7 @@
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
@@ -2370,7 +2347,7 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
@@ -2380,7 +2357,7 @@
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
@@ -2395,22 +2372,22 @@
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
@@ -2425,37 +2402,37 @@
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
@@ -2470,42 +2447,42 @@
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.3">
@@ -2525,12 +2502,12 @@
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.3">
@@ -2540,32 +2517,32 @@
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
@@ -2575,69 +2552,52 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B199" s="20"/>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="4" t="s">
-        <v>231</v>
-      </c>
+      <c r="A205" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
